--- a/doc/4、日常管理/DFDL33-SH8619版本发布记录/DFDL33-SH8619_BootV1.0.0.1_AppV1.0.0.4/DFDL33-SH8619 协议转换单元软件版本对照表.xlsx
+++ b/doc/4、日常管理/DFDL33-SH8619版本发布记录/DFDL33-SH8619_BootV1.0.0.1_AppV1.0.0.4/DFDL33-SH8619 协议转换单元软件版本对照表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Project\SVN\DFDL33-SH8619\doc\4、日常管理\DFDL33-SH8619版本发布记录\DFDL33-SH8619_BootV1.0.0.1_AppV1.0.0.4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B68A4907-6198-49B0-AA93-1662B97FC212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3526DB35-68B0-465B-A61F-637A7A9240F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="2775" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -212,7 +212,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>V1.0.0.103</t>
+    <t>V1.0.0.105</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -223,7 +223,8 @@
 5、修改645地址默认值为002026100001；
 6、修改时段控通信失败重试周期为1min；
 7、增加校准系数读取功能；
-8、调整周期抄读默认时间为0；</t>
+8、调整周期抄读默认时间为0；
+9、增加禾望逆变器协议库，完善奥克斯协议库。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -234,7 +235,8 @@
 4、全天候数据抄读与控制；
 5、默认645地址；
 6、时段控通信异常重发逻辑
-7、周期抄读。</t>
+7、周期抄读。
+8、新增逆变器测试；</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -504,7 +506,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -575,6 +577,9 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -598,12 +603,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1212,22 +1211,22 @@
     <row r="1" spans="1:7" s="2" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="18"/>
       <c r="B1" s="18"/>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
     </row>
     <row r="2" spans="1:7" s="3" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="27"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="28"/>
     </row>
     <row r="3" spans="1:7" s="8" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="s">
@@ -1250,8 +1249,8 @@
       </c>
       <c r="G3" s="7"/>
     </row>
-    <row r="4" spans="1:7" s="33" customFormat="1" ht="142.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="32"/>
+    <row r="4" spans="1:7" s="10" customFormat="1" ht="158.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="24"/>
       <c r="B4" s="23" t="s">
         <v>24</v>
       </c>
@@ -1259,7 +1258,7 @@
         <v>25</v>
       </c>
       <c r="D4" s="14">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="E4" s="21" t="s">
         <v>26</v>
@@ -1361,20 +1360,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
     </row>
     <row r="2" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="31"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="32"/>
     </row>
     <row r="3" spans="1:4" s="10" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
